--- a/results/section5.2/statistical_tests_results.xlsx
+++ b/results/section5.2/statistical_tests_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ym_ya\Desktop\windpower\Simulation code and data\5.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ym_ya\Desktop\Simulation code and data\results\section5.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E56B4B0-7173-49AF-93EC-048D715814E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2973F1-E626-46DE-9326-BAB6FDF97D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23400" windowHeight="14880" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RMSE_Shapiro" sheetId="1" r:id="rId1"/>
@@ -534,7 +534,7 @@
       <c r="B2" s="2">
         <v>0.80021777224676971</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>4.6838948576629677E-49</v>
       </c>
       <c r="D2" t="s">
@@ -551,7 +551,7 @@
       <c r="B3" s="2">
         <v>0.7885744676692632</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>5.4265006082497789E-50</v>
       </c>
       <c r="D3" t="s">
@@ -568,7 +568,7 @@
       <c r="B4" s="2">
         <v>0.80748468425754805</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>1.8965452575942849E-48</v>
       </c>
       <c r="D4" t="s">
@@ -585,7 +585,7 @@
       <c r="B5" s="2">
         <v>0.79617795335853858</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>2.191906515698132E-49</v>
       </c>
       <c r="D5" t="s">
@@ -602,7 +602,7 @@
       <c r="B6" s="2">
         <v>0.64834941624057474</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>8.2518780906924441E-59</v>
       </c>
       <c r="D6" t="s">
@@ -619,7 +619,7 @@
       <c r="B7" s="2">
         <v>0.69805503787831369</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>4.3185172876304333E-56</v>
       </c>
       <c r="D7" t="s">
@@ -636,7 +636,7 @@
       <c r="B8" s="2">
         <v>0.91121601363869198</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>1.175067805262197E-36</v>
       </c>
       <c r="D8" t="s">
@@ -653,7 +653,7 @@
       <c r="B9" s="2">
         <v>0.93127719995173963</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>3.9496261489728651E-33</v>
       </c>
       <c r="D9" t="s">
@@ -670,7 +670,7 @@
       <c r="B10" s="2">
         <v>0.88801263497682448</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>5.1504085362858592E-40</v>
       </c>
       <c r="D10" t="s">
@@ -967,7 +967,7 @@
       <c r="B2" s="2">
         <v>0.80021777224676971</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>4.6838948576629677E-49</v>
       </c>
       <c r="D2" t="s">
@@ -984,7 +984,7 @@
       <c r="B3" s="2">
         <v>0.7885744676692632</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>5.4265006082497789E-50</v>
       </c>
       <c r="D3" t="s">
@@ -1001,7 +1001,7 @@
       <c r="B4" s="2">
         <v>0.80748468425754805</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>1.8965452575942849E-48</v>
       </c>
       <c r="D4" t="s">
@@ -1018,7 +1018,7 @@
       <c r="B5" s="2">
         <v>0.79617795335853858</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>2.191906515698132E-49</v>
       </c>
       <c r="D5" t="s">
@@ -1035,7 +1035,7 @@
       <c r="B6" s="2">
         <v>0.64834941624057474</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>8.2518780906924441E-59</v>
       </c>
       <c r="D6" t="s">
@@ -1052,7 +1052,7 @@
       <c r="B7" s="2">
         <v>0.69805503787831369</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>4.3185172876304333E-56</v>
       </c>
       <c r="D7" t="s">
@@ -1069,7 +1069,7 @@
       <c r="B8" s="2">
         <v>0.91121601363869198</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>1.175067805262197E-36</v>
       </c>
       <c r="D8" t="s">
@@ -1086,7 +1086,7 @@
       <c r="B9" s="2">
         <v>0.93127719995173963</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>3.9496261489728651E-33</v>
       </c>
       <c r="D9" t="s">
@@ -1103,7 +1103,7 @@
       <c r="B10" s="2">
         <v>0.88801263497682448</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>5.1504085362858592E-40</v>
       </c>
       <c r="D10" t="s">
@@ -1396,7 +1396,7 @@
       <c r="B2" s="2">
         <v>0.66259631625496773</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>4.5809451626554838E-58</v>
       </c>
       <c r="D2" t="s">
@@ -1413,7 +1413,7 @@
       <c r="B3" s="2">
         <v>0.70088670606482095</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>6.3278894841900378E-56</v>
       </c>
       <c r="D3" t="s">
@@ -1430,7 +1430,7 @@
       <c r="B4" s="2">
         <v>0.67791066157769442</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>3.0989102887346139E-57</v>
       </c>
       <c r="D4" t="s">
@@ -1447,7 +1447,7 @@
       <c r="B5" s="2">
         <v>0.66867239802838108</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>9.6938840489177435E-58</v>
       </c>
       <c r="D5" t="s">
@@ -1464,7 +1464,7 @@
       <c r="B6" s="2">
         <v>0.50464612371577233</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>3.6448120227842271E-65</v>
       </c>
       <c r="D6" t="s">
@@ -1481,7 +1481,7 @@
       <c r="B7" s="2">
         <v>0.50981247943277164</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>5.7690145662253809E-65</v>
       </c>
       <c r="D7" t="s">
@@ -1498,7 +1498,7 @@
       <c r="B8" s="2">
         <v>0.70689180305644461</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>1.43725427358824E-55</v>
       </c>
       <c r="D8" t="s">
@@ -1515,7 +1515,7 @@
       <c r="B9" s="2">
         <v>0.89046186020991658</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>1.092198787961716E-39</v>
       </c>
       <c r="D9" t="s">
@@ -1532,7 +1532,7 @@
       <c r="B10" s="2">
         <v>0.80040496513771553</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>4.853126144034098E-49</v>
       </c>
       <c r="D10" t="s">
